--- a/results/Int All Data -0.9/Rando_3_permute.xlsx
+++ b/results/Int All Data -0.9/Rando_3_permute.xlsx
@@ -440,1313 +440,1313 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.8304472492392021</v>
+        <v>0.8403358625259754</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>accx_lineintegral</t>
+          <t>accz_lineintegral</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.8312126196067066</v>
+        <v>0.8432696650238405</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_5</t>
+          <t>scl_std</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.8297942574711544</v>
+        <v>0.8427988707973217</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>accy_kurtosis</t>
+          <t>scr_svd_entropy</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.8276207252165618</v>
+        <v>0.8409786540455593</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>scl_min</t>
+          <t>accx_min</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.8284184549929865</v>
+        <v>0.8465891424334557</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>scl_ptp</t>
+          <t>scl_kurtosis</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.8262449227383939</v>
+        <v>0.8465516829003035</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>bvp_kurtosis</t>
+          <t>accx_svd_entropy</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.827824202586783</v>
+        <v>0.8433020244327607</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>accz_n_sign_changes</t>
+          <t>scl_skewness</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.8301475729739844</v>
+        <v>0.8419100422501327</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>bvp_lineintegral</t>
+          <t>accz_skewness</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.8302974111065933</v>
+        <v>0.8432645648996084</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="inlineStr">
         <is>
-          <t>bvp_energy</t>
+          <t>accy_perm_entropy</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.8330651957673894</v>
+        <v>0.8467602603947566</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>hrv_sum</t>
+          <t>accx_rms</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.8328242588640159</v>
+        <v>0.8359989982652543</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="1" t="inlineStr">
         <is>
-          <t>bvp_svd_entropy</t>
+          <t>hrv_energy</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.8320427087920514</v>
+        <v>0.8354047458590508</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>accx_rms</t>
+          <t>scr_iqr</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>0.8272776099621958</v>
+        <v>0.833343592203915</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="1" t="inlineStr">
         <is>
-          <t>bvp_perm_entropy</t>
+          <t>hrv_lineintegral</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>0.825607231343042</v>
+        <v>0.8368980270609074</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_above_mean</t>
+          <t>accz_rms</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8268280955643692</v>
+        <v>0.835613323353504</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="1" t="inlineStr">
         <is>
-          <t>scl_entropy</t>
+          <t>scl_pct_5</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8264747800615392</v>
+        <v>0.8336219886404406</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="1" t="inlineStr">
         <is>
-          <t>accz_std</t>
+          <t>bvp_iqr</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8290016278189618</v>
+        <v>0.8351263494225252</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr_5_95</t>
+          <t>accx_mean</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.8291889254847229</v>
+        <v>0.8233638801463771</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="1" t="inlineStr">
         <is>
-          <t>hrv_std</t>
+          <t>accy_std</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.8316084947669208</v>
+        <v>0.8172553382472738</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="1" t="inlineStr">
         <is>
-          <t>accy_max</t>
+          <t>accy_mean</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.8037313915812073</v>
+        <v>0.8127260761965595</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" s="1" t="inlineStr">
         <is>
-          <t>accy_n_below_mean</t>
+          <t>accy_peaks</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.7957915533501133</v>
+        <v>0.8109382188537172</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="1" t="inlineStr">
         <is>
-          <t>hrv_peaks</t>
+          <t>scr_n_below_mean</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.7955131569135877</v>
+        <v>0.8122178224368886</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>bvp_mean</t>
+          <t>bvp_skewness</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.7955131569135877</v>
+        <v>0.8148570487937679</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="1" t="inlineStr">
         <is>
-          <t>scl_max</t>
+          <t>scr_energy</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.7971460759995892</v>
+        <v>0.8158046167028014</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="1" t="inlineStr">
         <is>
-          <t>accx_kurtosis</t>
+          <t>accz_n_sign_changes</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.7988913736850474</v>
+        <v>0.8134650666111398</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="1" t="inlineStr">
         <is>
-          <t>scr_min</t>
+          <t>accx_energy</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.7988913736850474</v>
+        <v>0.8075327427975694</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>bvp_max</t>
+          <t>accy_energy</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.8005081130665886</v>
+        <v>0.8048560569075379</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="1" t="inlineStr">
         <is>
-          <t>accz_n_above_mean</t>
+          <t>hrv_iqr_5_95</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.7950849223444533</v>
+        <v>0.8008886878541068</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="1" t="inlineStr">
         <is>
-          <t>bvp_entropy</t>
+          <t>accy_min</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.7950849223444533</v>
+        <v>0.802784703003938</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_below_mean</t>
+          <t>scl_iqr</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>0.7968514998586035</v>
+        <v>0.8023939279679557</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="1" t="inlineStr">
         <is>
-          <t>accx_std</t>
+          <t>hrv_sum</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>0.7957004545793488</v>
+        <v>0.8022815493684992</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="1" t="inlineStr">
         <is>
-          <t>scl_mean</t>
+          <t>scl_min</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>0.8019000952492167</v>
+        <v>0.7995886837740076</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="1" t="inlineStr">
         <is>
-          <t>accx_max</t>
+          <t>accx_ptp</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>0.807816239358327</v>
+        <v>0.7982665205334519</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="1" t="inlineStr">
         <is>
-          <t>accz_entropy</t>
+          <t>bvp_mean</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>0.8082444739274615</v>
+        <v>0.7982665205334519</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_above_mean</t>
+          <t>scr_n_sign_changes</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>0.8044754821200196</v>
+        <v>0.7982665205334519</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="1" t="inlineStr">
         <is>
-          <t>scl_peaks</t>
+          <t>accy_svd_entropy</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>0.8044754821200196</v>
+        <v>0.7907659964517204</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="1" t="inlineStr">
         <is>
-          <t>scl_svd_entropy</t>
+          <t>accx_n_sign_changes</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>0.8019324546581369</v>
+        <v>0.7907072570898761</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="1" t="inlineStr">
         <is>
-          <t>accx_skewness</t>
+          <t>scl_svd_entropy</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>0.8028800225671704</v>
+        <v>0.7899257070179116</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="1" t="inlineStr">
         <is>
-          <t>accz_skewness</t>
+          <t>accy_skewness</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>0.8012096439480167</v>
+        <v>0.7919119416067432</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="1" t="inlineStr">
         <is>
-          <t>accz_pct_95</t>
+          <t>scl_energy</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>0.8000432982960661</v>
+        <v>0.7913551487336919</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="1" t="inlineStr">
         <is>
-          <t>scr_svd_entropy</t>
+          <t>scl_ptp</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>0.7999147399921493</v>
+        <v>0.7940267344994913</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="1" t="inlineStr">
         <is>
-          <t>accz_max</t>
+          <t>bvp_pct_5</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>0.8134123067052916</v>
+        <v>0.7923725355847978</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="1" t="inlineStr">
         <is>
-          <t>accz_svd_entropy</t>
+          <t>scr_std</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>0.8102162874753611</v>
+        <v>0.7945622475438505</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="1" t="inlineStr">
         <is>
-          <t>hrv_rms</t>
+          <t>bvp_max</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>0.8166832450015264</v>
+        <v>0.7906272378993398</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="1" t="inlineStr">
         <is>
-          <t>scl_std</t>
+          <t>scr_entropy</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>0.8201312807150585</v>
+        <v>0.7906272378993398</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="1" t="inlineStr">
         <is>
-          <t>scr_mean</t>
+          <t>accz_kurtosis</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>0.8225193699201003</v>
+        <v>0.7906272378993398</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="1" t="inlineStr">
         <is>
-          <t>accz_lineintegral</t>
+          <t>accy_rms</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>0.8177227910130886</v>
+        <v>0.7846685341328452</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="1" t="inlineStr">
         <is>
-          <t>accz_energy</t>
+          <t>hrv_pct_95</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>0.8121021023767283</v>
+        <v>0.7855250032711141</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="1" t="inlineStr">
         <is>
-          <t>accz_ptp</t>
+          <t>accy_ptp</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>0.8014540981784466</v>
+        <v>0.7828108578479305</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="1" t="inlineStr">
         <is>
-          <t>bvp_min</t>
+          <t>accz_svd_entropy</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>0.808777524842881</v>
+        <v>0.7819007494720492</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="1" t="inlineStr">
         <is>
-          <t>scl_n_above_mean</t>
+          <t>scl_iqr_5_95</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>0.8080334343040687</v>
+        <v>0.7892412351727078</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="1" t="inlineStr">
         <is>
-          <t>accx_mean</t>
+          <t>scl_perm_entropy</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>0.8066141928367524</v>
+        <v>0.7912274697615393</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
         <is>
-          <t>accy_min</t>
+          <t>scr_peaks</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>0.7890395164660149</v>
+        <v>0.7912274697615393</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_95</t>
+          <t>accy_pct_5</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>0.7921444369251808</v>
+        <v>0.7989152915090318</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="1" t="inlineStr">
         <is>
-          <t>bvp_rms</t>
+          <t>scl_pct_95</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>0.7929098072926852</v>
+        <v>0.7908528744300172</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="1" t="inlineStr">
         <is>
-          <t>hrv_min</t>
+          <t>accz_sum</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>0.7946125453207591</v>
+        <v>0.7912019691403793</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="1" t="inlineStr">
         <is>
-          <t>scl_lineintegral</t>
+          <t>accz_energy</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>0.79234281417117</v>
+        <v>0.7931831036049788</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr</t>
+          <t>hrv_svd_entropy</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>0.7930869047099823</v>
+        <v>0.7935313189835769</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="1" t="inlineStr">
         <is>
-          <t>accx_peaks</t>
+          <t>accz_iqr</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>0.7930869047099823</v>
+        <v>0.7927923285689966</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="1" t="inlineStr">
         <is>
-          <t>accz_peaks</t>
+          <t>hrv_n_below_mean</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>0.7675298304507665</v>
+        <v>0.7875351556839302</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="1" t="inlineStr">
         <is>
-          <t>accy_rms</t>
+          <t>scr_pct_5</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>0.6977742002653471</v>
+        <v>0.787150360103944</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="1" t="inlineStr">
         <is>
-          <t>accz_n_below_mean</t>
+          <t>hrv_skewness</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>0.6960825418175014</v>
+        <v>0.7879693697090607</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_5</t>
+          <t>accx_n_above_mean</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>0.7096268889804958</v>
+        <v>0.7876484136151509</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr_5_95</t>
+          <t>bvp_std</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>0.7141399713267498</v>
+        <v>0.7899828635825805</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="1" t="inlineStr">
         <is>
-          <t>scl_energy</t>
+          <t>scr_n_above_mean</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>0.7066718066539386</v>
+        <v>0.7896295480797504</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="1" t="inlineStr">
         <is>
-          <t>bvp_skewness</t>
+          <t>accx_iqr</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>0.7062222922561121</v>
+        <v>0.789891764811816</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_sign_changes</t>
+          <t>accx_lineintegral</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>0.7062222922561121</v>
+        <v>0.7972688307138627</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr</t>
+          <t>accy_lineintegral</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>0.717972802620268</v>
+        <v>0.816021811648543</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="1" t="inlineStr">
         <is>
-          <t>hrv_entropy</t>
+          <t>accx_kurtosis</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>0.665023136977378</v>
+        <v>0.8165786045215943</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_5</t>
+          <t>scl_peaks</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>0.6549957651382239</v>
+        <v>0.816021811648543</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="1" t="inlineStr">
         <is>
-          <t>bvp_sum</t>
+          <t>hrv_kurtosis</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>0.6547173687016983</v>
+        <v>0.816021811648543</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="1" t="inlineStr">
         <is>
-          <t>accy_mean</t>
+          <t>hrv_max</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>0.6486624660402073</v>
+        <v>0.8195285867239194</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr</t>
+          <t>hrv_n_sign_changes</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>0.6594875676557859</v>
+        <v>0.8195285867239194</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_5</t>
+          <t>accz_entropy</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>0.6164622161692932</v>
+        <v>0.82274078565831</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_5</t>
+          <t>bvp_entropy</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>0.6210127580486995</v>
+        <v>0.82274078565831</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" s="1" t="inlineStr">
         <is>
-          <t>scl_n_below_mean</t>
+          <t>hrv_mean</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>0.6427046416054769</v>
+        <v>0.8220179749481897</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="1" t="inlineStr">
         <is>
-          <t>hrv_iqr_5_95</t>
+          <t>bvp_kurtosis</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>0.6346584042309223</v>
+        <v>0.8259742644213927</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="1" t="inlineStr">
         <is>
-          <t>scr_peaks</t>
+          <t>accx_std</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>0.6346584042309223</v>
+        <v>0.8317184112374378</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="1" t="inlineStr">
         <is>
-          <t>scl_rms</t>
+          <t>scr_min</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>0.6369341148365076</v>
+        <v>0.8317184112374378</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="1" t="inlineStr">
         <is>
-          <t>accy_std</t>
+          <t>accx_perm_entropy</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>0.6741667803935748</v>
+        <v>0.8262781614790782</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="1" t="inlineStr">
         <is>
-          <t>bvp_std</t>
+          <t>scr_skewness</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>0.623866541356028</v>
+        <v>0.825202035266128</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr_5_95</t>
+          <t>scl_sum</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>0.6156279061914804</v>
+        <v>0.8225628089092487</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="1" t="inlineStr">
         <is>
-          <t>accx_n_below_mean</t>
+          <t>accz_mean</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>0.6077527867782269</v>
+        <v>0.7986404123995627</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="1" t="inlineStr">
         <is>
-          <t>accx_n_sign_changes</t>
+          <t>accy_pct_95</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>0.5965105301737419</v>
+        <v>0.6911836086931442</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="1" t="inlineStr">
         <is>
-          <t>accz_perm_entropy</t>
+          <t>scr_iqr_5_95</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>0.5881322571250494</v>
+        <v>0.6873558775238581</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="1" t="inlineStr">
         <is>
-          <t>hrv_mean</t>
+          <t>accz_perm_entropy</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>0.5667511294137179</v>
+        <v>0.6476371652032241</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="1" t="inlineStr">
         <is>
-          <t>accy_iqr_5_95</t>
+          <t>bvp_n_above_mean</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>0.5567773968121762</v>
+        <v>0.656760408122493</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="1" t="inlineStr">
         <is>
-          <t>accx_perm_entropy</t>
+          <t>hrv_n_above_mean</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>0.5534315394496367</v>
+        <v>0.6542173806606103</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="1" t="inlineStr">
         <is>
-          <t>scr_iqr</t>
+          <t>bvp_peaks</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.5352626106726959</v>
+        <v>0.6552560473404083</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" s="1" t="inlineStr">
         <is>
-          <t>scl_skewness</t>
+          <t>scr_pct_95</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.533383654559089</v>
+        <v>0.6569587853684822</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="1" t="inlineStr">
         <is>
-          <t>accz_mean</t>
+          <t>scl_max</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.5184694843739228</v>
+        <v>0.6552347675117163</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" s="1" t="inlineStr">
         <is>
-          <t>hrv_svd_entropy</t>
+          <t>bvp_n_sign_changes</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.5248240633006316</v>
+        <v>0.6443620061145214</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr_5_95</t>
+          <t>accx_skewness</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.5220562786398355</v>
+        <v>0.6455879704600804</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="1" t="inlineStr">
         <is>
-          <t>hrv_ptp</t>
+          <t>scl_rms</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.5216655036038533</v>
+        <v>0.6397425246248067</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="1" t="inlineStr">
         <is>
-          <t>scl_perm_entropy</t>
+          <t>accx_n_below_mean</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.5202897011256854</v>
+        <v>0.6505514465359252</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="1" t="inlineStr">
         <is>
-          <t>accy_ptp</t>
+          <t>bvp_perm_entropy</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.5123558423505875</v>
+        <v>0.6399885616524121</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="1" t="inlineStr">
         <is>
-          <t>accx_min</t>
+          <t>bvp_energy</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.5123558423505875</v>
+        <v>0.618012302203113</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="1" t="inlineStr">
         <is>
-          <t>accx_svd_entropy</t>
+          <t>accz_pct_95</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.5123558423505875</v>
+        <v>0.5825785735691162</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="1" t="inlineStr">
         <is>
-          <t>accy_sum</t>
+          <t>accz_n_below_mean</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.5057228669873531</v>
+        <v>0.5817859439169235</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="1" t="inlineStr">
         <is>
-          <t>scr_skewness</t>
+          <t>bvp_lineintegral</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.5057228669873531</v>
+        <v>0.5582636433599196</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="1" t="inlineStr">
         <is>
-          <t>hrv_skewness</t>
+          <t>accz_pct_5</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.5054070110176753</v>
+        <v>0.5379850218144624</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" s="1" t="inlineStr">
         <is>
-          <t>scr_n_below_mean</t>
+          <t>hrv_perm_entropy</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.5054070110176753</v>
+        <v>0.5399388969943737</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" s="1" t="inlineStr">
         <is>
-          <t>scr_n_above_mean</t>
+          <t>bvp_iqr_5_95</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.5041061276058117</v>
+        <v>0.5236906046566596</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" s="1" t="inlineStr">
         <is>
-          <t>scr_perm_entropy</t>
+          <t>scr_sum</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.5041061276058117</v>
+        <v>0.5125011079580228</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" s="1" t="inlineStr">
         <is>
-          <t>accz_iqr_5_95</t>
+          <t>hrv_peaks</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.5098289945931649</v>
+        <v>0.5059217718324007</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" s="1" t="inlineStr">
         <is>
-          <t>hrv_lineintegral</t>
+          <t>bvp_svd_entropy</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.5183571057744661</v>
+        <v>0.5127369447371642</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" s="1" t="inlineStr">
         <is>
-          <t>scr_sum</t>
+          <t>accy_max</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.5183571057744661</v>
+        <v>0.5376964251294728</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" s="1" t="inlineStr">
         <is>
-          <t>hrv_kurtosis</t>
+          <t>scr_max</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.5183945653076184</v>
+        <v>0.5379969807264546</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" s="1" t="inlineStr">
         <is>
-          <t>scr_lineintegral</t>
+          <t>scr_mean</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.5113708149084017</v>
+        <v>0.5430132167081477</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="1" t="inlineStr">
         <is>
-          <t>scl_sum</t>
+          <t>accy_entropy</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.5120025268477574</v>
+        <v>0.542734820271622</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="1" t="inlineStr">
         <is>
-          <t>scr_n_sign_changes</t>
+          <t>accy_sum</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.5120025268477574</v>
+        <v>0.5072678528969409</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" s="1" t="inlineStr">
         <is>
-          <t>accx_energy</t>
+          <t>bvp_n_below_mean</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.5113708149084017</v>
+        <v>0.5051521806724285</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" s="1" t="inlineStr">
         <is>
-          <t>bvp_iqr</t>
+          <t>accx_max</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.5116866708780796</v>
+        <v>0.5099436594552083</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="1" t="inlineStr">
         <is>
-          <t>bvp_ptp</t>
+          <t>accz_iqr_5_95</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>0.5054070110176753</v>
+        <v>0.507651769145163</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="1" t="inlineStr">
         <is>
-          <t>accy_svd_entropy</t>
+          <t>scr_ptp</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>0.5050911550479974</v>
+        <v>0.4943645385900021</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="1" t="inlineStr">
         <is>
-          <t>accy_perm_entropy</t>
+          <t>accy_n_above_mean</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>0.5035118751996083</v>
+        <v>0.4868469554720464</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" s="1" t="inlineStr">
         <is>
-          <t>accz_min</t>
+          <t>scr_kurtosis</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>0.5085655707144535</v>
+        <v>0.4847858018169105</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" s="1" t="inlineStr">
         <is>
-          <t>accx_pct_5</t>
+          <t>scl_n_above_mean</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>0.5107765625021984</v>
+        <v>0.4843950267809282</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" s="1" t="inlineStr">
         <is>
-          <t>scr_rms</t>
+          <t>scr_lineintegral</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>0.5107765625021984</v>
+        <v>0.4830881639130685</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" s="1" t="inlineStr">
         <is>
-          <t>accy_energy</t>
+          <t>accy_n_below_mean</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>0.5061511015564876</v>
+        <v>0.5134606347790486</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" s="1" t="inlineStr">
         <is>
-          <t>accx_n_above_mean</t>
+          <t>hrv_min</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>0.5061511015564876</v>
+        <v>0.5070311367860354</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" s="1" t="inlineStr">
         <is>
-          <t>bvp_pct_95</t>
+          <t>accx_pct_5</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>0.506392038459861</v>
+        <v>0.4965686715899866</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" s="1" t="inlineStr">
         <is>
-          <t>accx_iqr</t>
+          <t>accz_max</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>0.5069488313329122</v>
+        <v>0.4984300410683107</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" s="1" t="inlineStr">
         <is>
-          <t>hrv_perm_entropy</t>
+          <t>accz_min</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>0.5069488313329122</v>
+        <v>0.5041043689422835</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="1" t="inlineStr">
         <is>
-          <t>accx_sum</t>
+          <t>accx_peaks</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>0.5066329753632344</v>
+        <v>0.5030980616714057</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="1" t="inlineStr">
         <is>
-          <t>scl_n_sign_changes</t>
+          <t>accz_ptp</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>0.5075805432722679</v>
+        <v>0.5011390863672625</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="1" t="inlineStr">
         <is>
-          <t>scr_entropy</t>
+          <t>scl_n_sign_changes</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>0.5075805432722679</v>
+        <v>0.5011390863672625</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" s="1" t="inlineStr">
         <is>
-          <t>accy_n_sign_changes</t>
+          <t>bvp_sum</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>0.5069488313329122</v>
+        <v>0.5011390863672625</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_5</t>
+          <t>accz_peaks</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>0.5015792798483891</v>
+        <v>0.5025472482543506</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" s="1" t="inlineStr">
         <is>
-          <t>bvp_peaks</t>
+          <t>accy_iqr_5_95</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>0.5015792798483891</v>
+        <v>0.5067129945537707</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" s="1" t="inlineStr">
         <is>
-          <t>accy_entropy</t>
+          <t>hrv_entropy</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>0.5015792798483891</v>
+        <v>0.5059314444818063</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" s="1" t="inlineStr">
         <is>
-          <t>scr_pct_95</t>
+          <t>accy_iqr</t>
         </is>
       </c>
       <c r="B133" t="n">
@@ -1756,7 +1756,7 @@
     <row r="134">
       <c r="A134" s="1" t="inlineStr">
         <is>
-          <t>accy_skewness</t>
+          <t>scl_n_below_mean</t>
         </is>
       </c>
       <c r="B134" t="n">
@@ -1766,27 +1766,27 @@
     <row r="135">
       <c r="A135" s="1" t="inlineStr">
         <is>
-          <t>hrv_energy</t>
+          <t>accx_pct_95</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>0.5003158559696779</v>
+        <v>0.5000374595331523</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" s="1" t="inlineStr">
         <is>
-          <t>hrv_max</t>
+          <t>accx_iqr_5_95</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>0.5</v>
+        <v>0.50035331550283</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" s="1" t="inlineStr">
         <is>
-          <t>accy_peaks</t>
+          <t>hrv_pct_5</t>
         </is>
       </c>
       <c r="B137" t="n">
@@ -1796,17 +1796,17 @@
     <row r="138">
       <c r="A138" s="1" t="inlineStr">
         <is>
-          <t>hrv_n_below_mean</t>
+          <t>accz_std</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>0.5</v>
+        <v>0.5003158559696779</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" s="1" t="inlineStr">
         <is>
-          <t>hrv_pct_95</t>
+          <t>accz_n_above_mean</t>
         </is>
       </c>
       <c r="B139" t="n">
@@ -1816,7 +1816,7 @@
     <row r="140">
       <c r="A140" s="1" t="inlineStr">
         <is>
-          <t>accz_rms</t>
+          <t>hrv_std</t>
         </is>
       </c>
       <c r="B140" t="n">
@@ -1826,7 +1826,7 @@
     <row r="141">
       <c r="A141" s="1" t="inlineStr">
         <is>
-          <t>scr_ptp</t>
+          <t>accx_entropy</t>
         </is>
       </c>
       <c r="B141" t="n">
@@ -1836,7 +1836,7 @@
     <row r="142">
       <c r="A142" s="1" t="inlineStr">
         <is>
-          <t>bvp_n_sign_changes</t>
+          <t>hrv_iqr</t>
         </is>
       </c>
       <c r="B142" t="n">
@@ -1846,7 +1846,7 @@
     <row r="143">
       <c r="A143" s="1" t="inlineStr">
         <is>
-          <t>scl_iqr</t>
+          <t>accy_kurtosis</t>
         </is>
       </c>
       <c r="B143" t="n">
@@ -1856,7 +1856,7 @@
     <row r="144">
       <c r="A144" s="1" t="inlineStr">
         <is>
-          <t>accx_entropy</t>
+          <t>hrv_rms</t>
         </is>
       </c>
       <c r="B144" t="n">
@@ -1866,7 +1866,7 @@
     <row r="145">
       <c r="A145" s="1" t="inlineStr">
         <is>
-          <t>accz_kurtosis</t>
+          <t>scl_entropy</t>
         </is>
       </c>
       <c r="B145" t="n">
@@ -1876,7 +1876,7 @@
     <row r="146">
       <c r="A146" s="1" t="inlineStr">
         <is>
-          <t>accz_sum</t>
+          <t>hrv_ptp</t>
         </is>
       </c>
       <c r="B146" t="n">
@@ -1886,7 +1886,7 @@
     <row r="147">
       <c r="A147" s="1" t="inlineStr">
         <is>
-          <t>scl_pct_95</t>
+          <t>bvp_ptp</t>
         </is>
       </c>
       <c r="B147" t="n">
@@ -1896,7 +1896,7 @@
     <row r="148">
       <c r="A148" s="1" t="inlineStr">
         <is>
-          <t>scr_kurtosis</t>
+          <t>bvp_pct_95</t>
         </is>
       </c>
       <c r="B148" t="n">
@@ -1906,7 +1906,7 @@
     <row r="149">
       <c r="A149" s="1" t="inlineStr">
         <is>
-          <t>accy_lineintegral</t>
+          <t>scl_lineintegral</t>
         </is>
       </c>
       <c r="B149" t="n">
@@ -1916,7 +1916,7 @@
     <row r="150">
       <c r="A150" s="1" t="inlineStr">
         <is>
-          <t>accy_pct_95</t>
+          <t>bvp_rms</t>
         </is>
       </c>
       <c r="B150" t="n">
@@ -1926,7 +1926,7 @@
     <row r="151">
       <c r="A151" s="1" t="inlineStr">
         <is>
-          <t>scr_max</t>
+          <t>bvp_min</t>
         </is>
       </c>
       <c r="B151" t="n">
@@ -1936,7 +1936,7 @@
     <row r="152">
       <c r="A152" s="1" t="inlineStr">
         <is>
-          <t>scr_energy</t>
+          <t>scr_rms</t>
         </is>
       </c>
       <c r="B152" t="n">
@@ -1946,7 +1946,7 @@
     <row r="153">
       <c r="A153" s="1" t="inlineStr">
         <is>
-          <t>accx_ptp</t>
+          <t>accy_n_sign_changes</t>
         </is>
       </c>
       <c r="B153" t="n">
@@ -1956,7 +1956,7 @@
     <row r="154">
       <c r="A154" s="1" t="inlineStr">
         <is>
-          <t>scl_kurtosis</t>
+          <t>accx_sum</t>
         </is>
       </c>
       <c r="B154" t="n">
@@ -1966,7 +1966,7 @@
     <row r="155">
       <c r="A155" s="1" t="inlineStr">
         <is>
-          <t>accy_n_above_mean</t>
+          <t>scr_perm_entropy</t>
         </is>
       </c>
       <c r="B155" t="n">
@@ -1976,7 +1976,7 @@
     <row r="156">
       <c r="A156" s="1" t="inlineStr">
         <is>
-          <t>scr_std</t>
+          <t>scl_mean</t>
         </is>
       </c>
       <c r="B156" t="n">
